--- a/docs/workbook-split/dateien/Projekte.xlsx
+++ b/docs/workbook-split/dateien/Projekte.xlsx
@@ -717,25 +717,30 @@
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C7,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C7,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M7" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C7,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C7,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N7" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C7,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C7,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O7" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C7,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C7,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P7" s="7">
-        <f>IF(ISNUMBER(L7),IF(L7=0,"n.a.",N7/L7),"n.a.")</f>
-        <v/>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q7" s="1" t="n"/>
     </row>
@@ -775,25 +780,30 @@
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C8,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C8,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M8" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C8,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C8,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N8" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C8,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C8,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O8" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C8,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C8,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P8" s="7">
-        <f>IF(ISNUMBER(L8),IF(L8=0,"n.a.",N8/L8),"n.a.")</f>
-        <v/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q8" s="1" t="n"/>
     </row>
@@ -829,25 +839,20 @@
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C9,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C9,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M9" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C9,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C9,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N9" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C9,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C9,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O9" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C9,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C9,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P9" s="7">
-        <f>IF(ISNUMBER(L9),IF(L9=0,"n.a.",N9/L9),"n.a.")</f>
-        <v/>
+      <c r="L9" s="6" t="n">
+        <v>124.95</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>-1212.92</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>-1212.92</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>-1217.49</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>-9.707242897158864</v>
       </c>
       <c r="Q9" s="1" t="n"/>
     </row>
@@ -883,25 +888,20 @@
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L10" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C10,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C10,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M10" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C10,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C10,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N10" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C10,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C10,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O10" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C10,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C10,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P10" s="7">
-        <f>IF(ISNUMBER(L10),IF(L10=0,"n.a.",N10/L10),"n.a.")</f>
-        <v/>
+      <c r="L10" s="6" t="n">
+        <v>-35814.88</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>-35814.88</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>-35814.88</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>-35814.88</v>
+      </c>
+      <c r="P10" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="Q10" s="1" t="n"/>
     </row>
@@ -937,25 +937,22 @@
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C11,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C11,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M11" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C11,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C11,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N11" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C11,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C11,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O11" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C11,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C11,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P11" s="7">
-        <f>IF(ISNUMBER(L11),IF(L11=0,"n.a.",N11/L11),"n.a.")</f>
-        <v/>
+      <c r="L11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q11" s="1" t="n"/>
     </row>
@@ -991,25 +988,20 @@
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L12" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C12,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C12,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M12" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C12,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C12,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N12" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C12,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C12,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O12" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C12,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C12,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P12" s="7">
-        <f>IF(ISNUMBER(L12),IF(L12=0,"n.a.",N12/L12),"n.a.")</f>
-        <v/>
+      <c r="L12" s="6" t="n">
+        <v>40570.44</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>-22810.76</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>-22810.76</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>-24293.85</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>-0.562250742165971</v>
       </c>
       <c r="Q12" s="1" t="n"/>
     </row>
@@ -1045,25 +1037,20 @@
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C13,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C13,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M13" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C13,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C13,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N13" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C13,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C13,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O13" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C13,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C13,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P13" s="7">
-        <f>IF(ISNUMBER(L13),IF(L13=0,"n.a.",N13/L13),"n.a.")</f>
-        <v/>
+      <c r="L13" s="6" t="n">
+        <v>149536.25</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>143705.12</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>142168.39</v>
+      </c>
+      <c r="O13" s="6" t="n">
+        <v>136701.97</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>0.9507286025963605</v>
       </c>
       <c r="Q13" s="1" t="n"/>
     </row>
@@ -1099,25 +1086,20 @@
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C14,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C14,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M14" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C14,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C14,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N14" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C14,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C14,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O14" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C14,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C14,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P14" s="7">
-        <f>IF(ISNUMBER(L14),IF(L14=0,"n.a.",N14/L14),"n.a.")</f>
-        <v/>
+      <c r="L14" s="6" t="n">
+        <v>33120.57</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>21824.76</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>21824.76</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>20614.01</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>0.658948804323114</v>
       </c>
       <c r="Q14" s="1" t="n"/>
     </row>
@@ -1153,25 +1135,20 @@
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C15,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C15,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M15" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C15,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C15,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N15" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C15,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C15,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O15" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C15,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C15,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P15" s="7">
-        <f>IF(ISNUMBER(L15),IF(L15=0,"n.a.",N15/L15),"n.a.")</f>
-        <v/>
+      <c r="L15" s="6" t="n">
+        <v>41935.11</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>22043.26</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>22043.26</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>20510.29</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>0.5256516556174528</v>
       </c>
       <c r="Q15" s="1" t="n"/>
     </row>
@@ -1207,25 +1184,20 @@
       <c r="K16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C16,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C16,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M16" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C16,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C16,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N16" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C16,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C16,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O16" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C16,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C16,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P16" s="7">
-        <f>IF(ISNUMBER(L16),IF(L16=0,"n.a.",N16/L16),"n.a.")</f>
-        <v/>
+      <c r="L16" s="6" t="n">
+        <v>845407</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>155293.58</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>131801.34</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>100896.77</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0.1559028255029826</v>
       </c>
       <c r="Q16" s="1" t="n"/>
     </row>
@@ -1261,25 +1233,20 @@
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L17" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C17,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C17,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M17" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C17,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C17,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N17" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C17,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C17,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O17" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C17,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C17,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P17" s="7">
-        <f>IF(ISNUMBER(L17),IF(L17=0,"n.a.",N17/L17),"n.a.")</f>
-        <v/>
+      <c r="L17" s="6" t="n">
+        <v>57545.38</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>1289.01</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>1289.01</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>-814.61</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0.02239988683713619</v>
       </c>
       <c r="Q17" s="1" t="n"/>
     </row>
@@ -1315,25 +1282,20 @@
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C18,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C18,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M18" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C18,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C18,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N18" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C18,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C18,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O18" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C18,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C18,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P18" s="7">
-        <f>IF(ISNUMBER(L18),IF(L18=0,"n.a.",N18/L18),"n.a.")</f>
-        <v/>
+      <c r="L18" s="6" t="n">
+        <v>62025.81</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>9486.15</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>7534.94</v>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>5267.53</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>0.1214807190748496</v>
       </c>
       <c r="Q18" s="1" t="n"/>
     </row>
@@ -1369,25 +1331,20 @@
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C19,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C19,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M19" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C19,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C19,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N19" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C19,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C19,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O19" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C19,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C19,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P19" s="7">
-        <f>IF(ISNUMBER(L19),IF(L19=0,"n.a.",N19/L19),"n.a.")</f>
-        <v/>
+      <c r="L19" s="6" t="n">
+        <v>73270.25</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>-5545.48</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>-8850.290000000001</v>
+      </c>
+      <c r="O19" s="6" t="n">
+        <v>-11528.75</v>
+      </c>
+      <c r="P19" s="7" t="n">
+        <v>-0.1207896793036737</v>
       </c>
       <c r="Q19" s="1" t="n"/>
     </row>
@@ -1423,25 +1380,20 @@
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C20,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C20,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M20" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C20,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C20,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N20" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C20,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C20,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O20" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C20,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C20,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P20" s="7">
-        <f>IF(ISNUMBER(L20),IF(L20=0,"n.a.",N20/L20),"n.a.")</f>
-        <v/>
+      <c r="L20" s="6" t="n">
+        <v>249898.21</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>88298.14999999999</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>88298.14999999999</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>79162.91</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>0.3533364644748756</v>
       </c>
       <c r="Q20" s="1" t="n"/>
     </row>
@@ -1477,25 +1429,20 @@
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C21,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C21,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M21" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C21,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C21,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N21" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C21,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C21,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O21" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C21,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C21,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P21" s="7">
-        <f>IF(ISNUMBER(L21),IF(L21=0,"n.a.",N21/L21),"n.a.")</f>
-        <v/>
+      <c r="L21" s="6" t="n">
+        <v>84738.88</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>15739.97</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>15780.75</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>12683.05</v>
+      </c>
+      <c r="P21" s="7" t="n">
+        <v>0.1862279746911925</v>
       </c>
       <c r="Q21" s="1" t="n"/>
     </row>
@@ -1531,25 +1478,20 @@
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C22,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C22,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M22" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C22,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C22,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N22" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C22,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C22,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O22" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C22,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C22,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P22" s="7">
-        <f>IF(ISNUMBER(L22),IF(L22=0,"n.a.",N22/L22),"n.a.")</f>
-        <v/>
+      <c r="L22" s="6" t="n">
+        <v>121773.65</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>25547.17</v>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>19147.42</v>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>14695.88</v>
+      </c>
+      <c r="P22" s="7" t="n">
+        <v>0.1572377932335936</v>
       </c>
       <c r="Q22" s="1" t="n"/>
     </row>
@@ -1585,25 +1527,20 @@
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C23,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C23,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M23" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C23,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C23,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N23" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C23,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C23,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O23" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C23,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C23,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P23" s="7">
-        <f>IF(ISNUMBER(L23),IF(L23=0,"n.a.",N23/L23),"n.a.")</f>
-        <v/>
+      <c r="L23" s="6" t="n">
+        <v>53164.67</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>-164162.5</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>-173917.74</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>-175861.22</v>
+      </c>
+      <c r="P23" s="7" t="n">
+        <v>-3.271302916015467</v>
       </c>
       <c r="Q23" s="1" t="n"/>
     </row>
@@ -1639,25 +1576,20 @@
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C24,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C24,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M24" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C24,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C24,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N24" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C24,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C24,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O24" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C24,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C24,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P24" s="7">
-        <f>IF(ISNUMBER(L24),IF(L24=0,"n.a.",N24/L24),"n.a.")</f>
-        <v/>
+      <c r="L24" s="6" t="n">
+        <v>32751.02</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>32511.02</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>26919.28</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>25722.04</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>0.8219371488277312</v>
       </c>
       <c r="Q24" s="1" t="n"/>
     </row>
@@ -1693,25 +1625,20 @@
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C25,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C25,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M25" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C25,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C25,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N25" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C25,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C25,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O25" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C25,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C25,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P25" s="7">
-        <f>IF(ISNUMBER(L25),IF(L25=0,"n.a.",N25/L25),"n.a.")</f>
-        <v/>
+      <c r="L25" s="6" t="n">
+        <v>24410.59</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>8632.59</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>8632.59</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>7740.24</v>
+      </c>
+      <c r="P25" s="7" t="n">
+        <v>0.3536411860590015</v>
       </c>
       <c r="Q25" s="1" t="n"/>
     </row>
@@ -1747,25 +1674,30 @@
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C26,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C26,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M26" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C26,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C26,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N26" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C26,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C26,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O26" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C26,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C26,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P26" s="7">
-        <f>IF(ISNUMBER(L26),IF(L26=0,"n.a.",N26/L26),"n.a.")</f>
-        <v/>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q26" s="1" t="n"/>
     </row>
@@ -1801,25 +1733,30 @@
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C27,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C27,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M27" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C27,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C27,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N27" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C27,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C27,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O27" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C27,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C27,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P27" s="7">
-        <f>IF(ISNUMBER(L27),IF(L27=0,"n.a.",N27/L27),"n.a.")</f>
-        <v/>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P27" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q27" s="1" t="n"/>
     </row>
@@ -1855,25 +1792,30 @@
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C28,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C28,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M28" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C28,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C28,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N28" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C28,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C28,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O28" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C28,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C28,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P28" s="7">
-        <f>IF(ISNUMBER(L28),IF(L28=0,"n.a.",N28/L28),"n.a.")</f>
-        <v/>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q28" s="1" t="n"/>
     </row>
@@ -1909,25 +1851,30 @@
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C29,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C29,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M29" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C29,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C29,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N29" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C29,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C29,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O29" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C29,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C29,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P29" s="7">
-        <f>IF(ISNUMBER(L29),IF(L29=0,"n.a.",N29/L29),"n.a.")</f>
-        <v/>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P29" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q29" s="1" t="n"/>
     </row>
@@ -1963,25 +1910,30 @@
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C30,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C30,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M30" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C30,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C30,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N30" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C30,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C30,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O30" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C30,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C30,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P30" s="7">
-        <f>IF(ISNUMBER(L30),IF(L30=0,"n.a.",N30/L30),"n.a.")</f>
-        <v/>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q30" s="1" t="n"/>
     </row>
@@ -2017,25 +1969,30 @@
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C31,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C31,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M31" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C31,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C31,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N31" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C31,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C31,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O31" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C31,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C31,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P31" s="7">
-        <f>IF(ISNUMBER(L31),IF(L31=0,"n.a.",N31/L31),"n.a.")</f>
-        <v/>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q31" s="1" t="n"/>
     </row>
@@ -2071,25 +2028,30 @@
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C32,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C32,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M32" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C32,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C32,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N32" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C32,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C32,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O32" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C32,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C32,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P32" s="7">
-        <f>IF(ISNUMBER(L32),IF(L32=0,"n.a.",N32/L32),"n.a.")</f>
-        <v/>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q32" s="1" t="n"/>
     </row>
@@ -2125,25 +2087,20 @@
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C33,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C33,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M33" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C33,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C33,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N33" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C33,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C33,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O33" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C33,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C33,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P33" s="7">
-        <f>IF(ISNUMBER(L33),IF(L33=0,"n.a.",N33/L33),"n.a.")</f>
-        <v/>
+      <c r="L33" s="6" t="n">
+        <v>45582.42</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>45582.42</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>45582.42</v>
+      </c>
+      <c r="O33" s="6" t="n">
+        <v>43916.12</v>
+      </c>
+      <c r="P33" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="Q33" s="1" t="n"/>
     </row>
@@ -2179,25 +2136,30 @@
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C34,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C34,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M34" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C34,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C34,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N34" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C34,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C34,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O34" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C34,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C34,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P34" s="7">
-        <f>IF(ISNUMBER(L34),IF(L34=0,"n.a.",N34/L34),"n.a.")</f>
-        <v/>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q34" s="1" t="n"/>
     </row>
@@ -2233,25 +2195,30 @@
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C35,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C35,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M35" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C35,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C35,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N35" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C35,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C35,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O35" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C35,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C35,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P35" s="7">
-        <f>IF(ISNUMBER(L35),IF(L35=0,"n.a.",N35/L35),"n.a.")</f>
-        <v/>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q35" s="1" t="n"/>
     </row>
@@ -2287,25 +2254,30 @@
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C36,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C36,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M36" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C36,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C36,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N36" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C36,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C36,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O36" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C36,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C36,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P36" s="7">
-        <f>IF(ISNUMBER(L36),IF(L36=0,"n.a.",N36/L36),"n.a.")</f>
-        <v/>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q36" s="1" t="n"/>
     </row>
@@ -2341,25 +2313,30 @@
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C37,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C37,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M37" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C37,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C37,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N37" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C37,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C37,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O37" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C37,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C37,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P37" s="7">
-        <f>IF(ISNUMBER(L37),IF(L37=0,"n.a.",N37/L37),"n.a.")</f>
-        <v/>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q37" s="1" t="n"/>
     </row>
@@ -2395,25 +2372,30 @@
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C38,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C38,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M38" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C38,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C38,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N38" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C38,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C38,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O38" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C38,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C38,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P38" s="7">
-        <f>IF(ISNUMBER(L38),IF(L38=0,"n.a.",N38/L38),"n.a.")</f>
-        <v/>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q38" s="1" t="n"/>
     </row>
@@ -2449,25 +2431,30 @@
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C39,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C39,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M39" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C39,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C39,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N39" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C39,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C39,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O39" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C39,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C39,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P39" s="7">
-        <f>IF(ISNUMBER(L39),IF(L39=0,"n.a.",N39/L39),"n.a.")</f>
-        <v/>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q39" s="1" t="n"/>
     </row>
@@ -2503,25 +2490,30 @@
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C40,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C40,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M40" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C40,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C40,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N40" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C40,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C40,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O40" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C40,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C40,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P40" s="7">
-        <f>IF(ISNUMBER(L40),IF(L40=0,"n.a.",N40/L40),"n.a.")</f>
-        <v/>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q40" s="1" t="n"/>
     </row>
@@ -2557,25 +2549,20 @@
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C41,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C41,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M41" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C41,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C41,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N41" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C41,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C41,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O41" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C41,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C41,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P41" s="7">
-        <f>IF(ISNUMBER(L41),IF(L41=0,"n.a.",N41/L41),"n.a.")</f>
-        <v/>
+      <c r="L41" s="6" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>83.51000000000001</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>83.51000000000001</v>
+      </c>
+      <c r="O41" s="6" t="n">
+        <v>81.34</v>
+      </c>
+      <c r="P41" s="7" t="n">
+        <v>1.408025628055977</v>
       </c>
       <c r="Q41" s="1" t="n"/>
     </row>
@@ -2611,25 +2598,20 @@
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C42,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C42,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M42" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C42,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C42,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N42" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C42,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C42,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O42" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C42,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C42,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P42" s="7">
-        <f>IF(ISNUMBER(L42),IF(L42=0,"n.a.",N42/L42),"n.a.")</f>
-        <v/>
+      <c r="L42" s="6" t="n">
+        <v>36922.66</v>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>20040.45</v>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>19781.16</v>
+      </c>
+      <c r="O42" s="6" t="n">
+        <v>18431.42</v>
+      </c>
+      <c r="P42" s="7" t="n">
+        <v>0.5357457994629855</v>
       </c>
       <c r="Q42" s="1" t="n"/>
     </row>
@@ -2665,25 +2647,20 @@
       <c r="K43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C43,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C43,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M43" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C43,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C43,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N43" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C43,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C43,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O43" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C43,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C43,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P43" s="7">
-        <f>IF(ISNUMBER(L43),IF(L43=0,"n.a.",N43/L43),"n.a.")</f>
-        <v/>
+      <c r="L43" s="6" t="n">
+        <v>98022.87</v>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>61393.34</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>59677.4</v>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>56094.09</v>
+      </c>
+      <c r="P43" s="7" t="n">
+        <v>0.6088109846202219</v>
       </c>
       <c r="Q43" s="1" t="n"/>
     </row>
@@ -2719,25 +2696,30 @@
       <c r="K44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C44,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C44,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M44" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C44,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C44,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N44" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C44,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C44,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O44" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C44,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C44,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P44" s="7">
-        <f>IF(ISNUMBER(L44),IF(L44=0,"n.a.",N44/L44),"n.a.")</f>
-        <v/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q44" s="1" t="n"/>
     </row>
@@ -2773,25 +2755,30 @@
       <c r="K45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C45,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C45,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M45" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C45,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C45,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N45" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C45,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C45,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O45" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C45,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C45,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P45" s="7">
-        <f>IF(ISNUMBER(L45),IF(L45=0,"n.a.",N45/L45),"n.a.")</f>
-        <v/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q45" s="1" t="n"/>
     </row>
@@ -2827,25 +2814,20 @@
       <c r="K46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L46" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C46,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C46,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M46" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C46,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C46,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N46" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C46,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C46,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O46" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C46,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C46,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P46" s="7">
-        <f>IF(ISNUMBER(L46),IF(L46=0,"n.a.",N46/L46),"n.a.")</f>
-        <v/>
+      <c r="L46" s="6" t="n">
+        <v>48086.9</v>
+      </c>
+      <c r="M46" s="6" t="n">
+        <v>18445.31</v>
+      </c>
+      <c r="N46" s="6" t="n">
+        <v>16812.77</v>
+      </c>
+      <c r="O46" s="6" t="n">
+        <v>15054.91</v>
+      </c>
+      <c r="P46" s="7" t="n">
+        <v>0.3496330601473582</v>
       </c>
       <c r="Q46" s="1" t="n"/>
     </row>
@@ -2881,25 +2863,20 @@
       <c r="K47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L47" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C47,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C47,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M47" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C47,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C47,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N47" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C47,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C47,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O47" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C47,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C47,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P47" s="7">
-        <f>IF(ISNUMBER(L47),IF(L47=0,"n.a.",N47/L47),"n.a.")</f>
-        <v/>
+      <c r="L47" s="6" t="n">
+        <v>2639009.53</v>
+      </c>
+      <c r="M47" s="6" t="n">
+        <v>-152984.43</v>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>-197875.4</v>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>-294346.62</v>
+      </c>
+      <c r="P47" s="7" t="n">
+        <v>-0.07498093422951754</v>
       </c>
       <c r="Q47" s="1" t="n"/>
     </row>
@@ -2935,25 +2912,20 @@
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L48" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C48,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C48,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M48" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C48,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C48,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N48" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C48,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C48,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O48" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C48,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C48,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P48" s="7">
-        <f>IF(ISNUMBER(L48),IF(L48=0,"n.a.",N48/L48),"n.a.")</f>
-        <v/>
+      <c r="L48" s="6" t="n">
+        <v>1969.8</v>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>211.05</v>
+      </c>
+      <c r="N48" s="6" t="n">
+        <v>211.05</v>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>139.04</v>
+      </c>
+      <c r="P48" s="7" t="n">
+        <v>0.1071428571428572</v>
       </c>
       <c r="Q48" s="1" t="n"/>
     </row>
@@ -2989,25 +2961,22 @@
       <c r="K49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L49" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C49,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C49,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M49" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C49,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C49,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N49" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C49,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C49,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O49" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C49,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C49,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P49" s="7">
-        <f>IF(ISNUMBER(L49),IF(L49=0,"n.a.",N49/L49),"n.a.")</f>
-        <v/>
+      <c r="L49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>-400.43</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>-400.43</v>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>-400.43</v>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q49" s="1" t="n"/>
     </row>
@@ -3043,25 +3012,20 @@
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L50" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C50,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C50,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M50" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C50,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C50,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N50" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C50,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C50,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O50" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C50,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C50,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P50" s="7">
-        <f>IF(ISNUMBER(L50),IF(L50=0,"n.a.",N50/L50),"n.a.")</f>
-        <v/>
+      <c r="L50" s="6" t="n">
+        <v>832368.22</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>382351.49</v>
+      </c>
+      <c r="N50" s="6" t="n">
+        <v>368287.75</v>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>337859.83</v>
+      </c>
+      <c r="P50" s="7" t="n">
+        <v>0.4424577262212149</v>
       </c>
       <c r="Q50" s="1" t="n"/>
     </row>
@@ -3097,25 +3061,20 @@
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C51,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C51,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M51" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C51,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C51,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N51" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C51,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C51,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O51" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C51,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C51,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P51" s="7">
-        <f>IF(ISNUMBER(L51),IF(L51=0,"n.a.",N51/L51),"n.a.")</f>
-        <v/>
+      <c r="L51" s="6" t="n">
+        <v>99403.64</v>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>64078.74</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>60852.11</v>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>57218.33</v>
+      </c>
+      <c r="P51" s="7" t="n">
+        <v>0.6121718480329292</v>
       </c>
       <c r="Q51" s="1" t="n"/>
     </row>
@@ -3151,25 +3110,20 @@
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L52" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C52,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C52,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M52" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C52,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C52,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N52" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C52,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C52,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O52" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C52,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C52,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P52" s="7">
-        <f>IF(ISNUMBER(L52),IF(L52=0,"n.a.",N52/L52),"n.a.")</f>
-        <v/>
+      <c r="L52" s="6" t="n">
+        <v>156757.06</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>128415.69</v>
+      </c>
+      <c r="N52" s="6" t="n">
+        <v>126459.47</v>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>120729.08</v>
+      </c>
+      <c r="P52" s="7" t="n">
+        <v>0.8067226445813669</v>
       </c>
       <c r="Q52" s="1" t="n"/>
     </row>
@@ -3205,25 +3159,22 @@
       <c r="K53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L53" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C53,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C53,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M53" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C53,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C53,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N53" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C53,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C53,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O53" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C53,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C53,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P53" s="7">
-        <f>IF(ISNUMBER(L53),IF(L53=0,"n.a.",N53/L53),"n.a.")</f>
-        <v/>
+      <c r="L53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="6" t="n">
+        <v>-712.8</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>-1791.14</v>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>-1791.14</v>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q53" s="1" t="n"/>
     </row>
@@ -3259,25 +3210,30 @@
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L54" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C54,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C54,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M54" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C54,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C54,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N54" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C54,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C54,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O54" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C54,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C54,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P54" s="7">
-        <f>IF(ISNUMBER(L54),IF(L54=0,"n.a.",N54/L54),"n.a.")</f>
-        <v/>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q54" s="1" t="n"/>
     </row>
@@ -3313,25 +3269,30 @@
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L55" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C55,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C55,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M55" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C55,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C55,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N55" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C55,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C55,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O55" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C55,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C55,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P55" s="7">
-        <f>IF(ISNUMBER(L55),IF(L55=0,"n.a.",N55/L55),"n.a.")</f>
-        <v/>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="Q55" s="1" t="n"/>
     </row>
@@ -3367,25 +3328,20 @@
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L56" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C56,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C56,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M56" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C56,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C56,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N56" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C56,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C56,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O56" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C56,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C56,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P56" s="7">
-        <f>IF(ISNUMBER(L56),IF(L56=0,"n.a.",N56/L56),"n.a.")</f>
-        <v/>
+      <c r="L56" s="6" t="n">
+        <v>135971.81</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>35088.55</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>35088.55</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>30117.99</v>
+      </c>
+      <c r="P56" s="7" t="n">
+        <v>0.2580575341315233</v>
       </c>
       <c r="Q56" s="1" t="n"/>
     </row>
@@ -3421,25 +3377,20 @@
       <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L57" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C57,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C57,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M57" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C57,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C57,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N57" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C57,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C57,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O57" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C57,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C57,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P57" s="7">
-        <f>IF(ISNUMBER(L57),IF(L57=0,"n.a.",N57/L57),"n.a.")</f>
-        <v/>
+      <c r="L57" s="6" t="n">
+        <v>9829.799999999999</v>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v>-2456.59</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>-3182.96</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>-3542.3</v>
+      </c>
+      <c r="P57" s="7" t="n">
+        <v>-0.3238071985187898</v>
       </c>
       <c r="Q57" s="1" t="n"/>
     </row>
@@ -3475,25 +3426,20 @@
       <c r="K58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L58" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C58,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C58,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M58" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C58,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C58,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N58" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C58,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C58,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O58" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C58,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C58,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P58" s="7">
-        <f>IF(ISNUMBER(L58),IF(L58=0,"n.a.",N58/L58),"n.a.")</f>
-        <v/>
+      <c r="L58" s="6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>-37400.93</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>-40094.1</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>-40825.22</v>
+      </c>
+      <c r="P58" s="7" t="n">
+        <v>-2.004705</v>
       </c>
       <c r="Q58" s="1" t="n"/>
     </row>
@@ -3529,25 +3475,20 @@
       <c r="K59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L59" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C59,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C59,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M59" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C59,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C59,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N59" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C59,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C59,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O59" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C59,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C59,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P59" s="7">
-        <f>IF(ISNUMBER(L59),IF(L59=0,"n.a.",N59/L59),"n.a.")</f>
-        <v/>
+      <c r="L59" s="6" t="n">
+        <v>-6447.83</v>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>-6447.83</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>-6447.83</v>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>-6447.83</v>
+      </c>
+      <c r="P59" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="Q59" s="1" t="n"/>
     </row>
@@ -3583,25 +3524,20 @@
       <c r="K60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="L60" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C60,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C60,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M60" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C60,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C60,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N60" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C60,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C60,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O60" s="6">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C60,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C60,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P60" s="7">
-        <f>IF(ISNUMBER(L60),IF(L60=0,"n.a.",N60/L60),"n.a.")</f>
-        <v/>
+      <c r="L60" s="6" t="n">
+        <v>131609.09</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>39166.15</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>35750.88</v>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>30939.8</v>
+      </c>
+      <c r="P60" s="7" t="n">
+        <v>0.2716444586008459</v>
       </c>
       <c r="Q60" s="1" t="n"/>
     </row>
@@ -3635,25 +3571,30 @@
       <c r="K61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L61" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C61,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C61,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M61" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C61,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C61,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N61" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C61,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C61,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O61" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C61,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C61,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P61" s="10">
-        <f>IF(ISNUMBER(L61),IF(L61=0,"n.a.",N61/L61),"n.a.")</f>
-        <v/>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O61" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P61" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3686,25 +3627,30 @@
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L62" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C62,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C62,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M62" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C62,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C62,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N62" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C62,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C62,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O62" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C62,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C62,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P62" s="10">
-        <f>IF(ISNUMBER(L62),IF(L62=0,"n.a.",N62/L62),"n.a.")</f>
-        <v/>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N62" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O62" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P62" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3737,25 +3683,30 @@
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L63" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C63,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C63,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M63" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C63,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C63,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N63" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C63,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C63,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O63" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C63,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C63,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P63" s="10">
-        <f>IF(ISNUMBER(L63),IF(L63=0,"n.a.",N63/L63),"n.a.")</f>
-        <v/>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M63" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O63" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P63" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3788,25 +3739,30 @@
       <c r="K64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L64" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C64,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C64,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M64" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C64,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C64,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N64" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C64,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C64,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O64" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C64,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C64,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P64" s="10">
-        <f>IF(ISNUMBER(L64),IF(L64=0,"n.a.",N64/L64),"n.a.")</f>
-        <v/>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M64" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N64" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O64" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P64" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3839,25 +3795,30 @@
       <c r="K65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L65" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C65,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C65,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M65" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C65,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C65,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N65" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C65,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C65,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O65" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C65,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C65,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P65" s="10">
-        <f>IF(ISNUMBER(L65),IF(L65=0,"n.a.",N65/L65),"n.a.")</f>
-        <v/>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N65" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O65" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P65" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3890,25 +3851,20 @@
       <c r="K66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L66" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C66,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C66,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M66" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C66,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C66,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N66" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C66,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C66,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O66" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C66,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C66,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P66" s="10">
-        <f>IF(ISNUMBER(L66),IF(L66=0,"n.a.",N66/L66),"n.a.")</f>
-        <v/>
+      <c r="L66" s="9" t="n">
+        <v>248519.28</v>
+      </c>
+      <c r="M66" s="9" t="n">
+        <v>111099.49</v>
+      </c>
+      <c r="N66" s="9" t="n">
+        <v>110634.35</v>
+      </c>
+      <c r="O66" s="9" t="n">
+        <v>101549.52</v>
+      </c>
+      <c r="P66" s="10" t="n">
+        <v>0.4451741128495141</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3941,25 +3897,20 @@
       <c r="K67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L67" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C67,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C67,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M67" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C67,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C67,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N67" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C67,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C67,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O67" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C67,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C67,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P67" s="10">
-        <f>IF(ISNUMBER(L67),IF(L67=0,"n.a.",N67/L67),"n.a.")</f>
-        <v/>
+      <c r="L67" s="9" t="n">
+        <v>2069335.5</v>
+      </c>
+      <c r="M67" s="9" t="n">
+        <v>274456.43</v>
+      </c>
+      <c r="N67" s="9" t="n">
+        <v>253217.2</v>
+      </c>
+      <c r="O67" s="9" t="n">
+        <v>177570.89</v>
+      </c>
+      <c r="P67" s="10" t="n">
+        <v>0.1223664311562818</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3992,25 +3943,20 @@
       <c r="K68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C68,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C68,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M68" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C68,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C68,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N68" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C68,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C68,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O68" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C68,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C68,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P68" s="10">
-        <f>IF(ISNUMBER(L68),IF(L68=0,"n.a.",N68/L68),"n.a.")</f>
-        <v/>
+      <c r="L68" s="9" t="n">
+        <v>1061843.93</v>
+      </c>
+      <c r="M68" s="9" t="n">
+        <v>376655.78</v>
+      </c>
+      <c r="N68" s="9" t="n">
+        <v>375389.55</v>
+      </c>
+      <c r="O68" s="9" t="n">
+        <v>336572.95</v>
+      </c>
+      <c r="P68" s="10" t="n">
+        <v>0.3535261062329565</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -4047,25 +3993,22 @@
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L69" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C69,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C69,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M69" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C69,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C69,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N69" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C69,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C69,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O69" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C69,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C69,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P69" s="10">
-        <f>IF(ISNUMBER(L69),IF(L69=0,"n.a.",N69/L69),"n.a.")</f>
-        <v/>
+      <c r="L69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="9" t="n">
+        <v>-955.84</v>
+      </c>
+      <c r="O69" s="9" t="n">
+        <v>-955.84</v>
+      </c>
+      <c r="P69" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -4098,25 +4041,20 @@
       <c r="K70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L70" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C70,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C70,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M70" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C70,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C70,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N70" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C70,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C70,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O70" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C70,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C70,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P70" s="10">
-        <f>IF(ISNUMBER(L70),IF(L70=0,"n.a.",N70/L70),"n.a.")</f>
-        <v/>
+      <c r="L70" s="9" t="n">
+        <v>103280</v>
+      </c>
+      <c r="M70" s="9" t="n">
+        <v>33286.16</v>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>33286.16</v>
+      </c>
+      <c r="O70" s="9" t="n">
+        <v>29510.67</v>
+      </c>
+      <c r="P70" s="10" t="n">
+        <v>0.3222904725019365</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -4149,25 +4087,20 @@
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L71" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C71,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C71,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M71" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C71,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C71,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N71" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C71,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C71,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O71" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C71,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C71,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P71" s="10">
-        <f>IF(ISNUMBER(L71),IF(L71=0,"n.a.",N71/L71),"n.a.")</f>
-        <v/>
+      <c r="L71" s="9" t="n">
+        <v>273337.79</v>
+      </c>
+      <c r="M71" s="9" t="n">
+        <v>125885.42</v>
+      </c>
+      <c r="N71" s="9" t="n">
+        <v>122594.33</v>
+      </c>
+      <c r="O71" s="9" t="n">
+        <v>112602.24</v>
+      </c>
+      <c r="P71" s="10" t="n">
+        <v>0.4485085285865522</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -4200,25 +4133,20 @@
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C72,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C72,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M72" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C72,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C72,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N72" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C72,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C72,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O72" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C72,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C72,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P72" s="10">
-        <f>IF(ISNUMBER(L72),IF(L72=0,"n.a.",N72/L72),"n.a.")</f>
-        <v/>
+      <c r="L72" s="9" t="n">
+        <v>27473.13</v>
+      </c>
+      <c r="M72" s="9" t="n">
+        <v>22519.56</v>
+      </c>
+      <c r="N72" s="9" t="n">
+        <v>22519.56</v>
+      </c>
+      <c r="O72" s="9" t="n">
+        <v>21515.26</v>
+      </c>
+      <c r="P72" s="10" t="n">
+        <v>0.8196940064710501</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -4251,25 +4179,20 @@
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L73" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C73,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C73,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M73" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C73,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C73,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N73" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C73,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C73,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O73" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C73,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C73,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P73" s="10">
-        <f>IF(ISNUMBER(L73),IF(L73=0,"n.a.",N73/L73),"n.a.")</f>
-        <v/>
+      <c r="L73" s="9" t="n">
+        <v>32538</v>
+      </c>
+      <c r="M73" s="9" t="n">
+        <v>16619.55</v>
+      </c>
+      <c r="N73" s="9" t="n">
+        <v>16619.55</v>
+      </c>
+      <c r="O73" s="9" t="n">
+        <v>15430.1</v>
+      </c>
+      <c r="P73" s="10" t="n">
+        <v>0.5107735570717314</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -4302,25 +4225,20 @@
       <c r="K74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L74" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C74,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C74,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M74" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C74,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C74,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N74" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C74,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C74,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O74" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C74,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C74,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P74" s="10">
-        <f>IF(ISNUMBER(L74),IF(L74=0,"n.a.",N74/L74),"n.a.")</f>
-        <v/>
+      <c r="L74" s="9" t="n">
+        <v>37000</v>
+      </c>
+      <c r="M74" s="9" t="n">
+        <v>14347.44</v>
+      </c>
+      <c r="N74" s="9" t="n">
+        <v>14347.44</v>
+      </c>
+      <c r="O74" s="9" t="n">
+        <v>12994.87</v>
+      </c>
+      <c r="P74" s="10" t="n">
+        <v>0.3877686486486487</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -4353,25 +4271,20 @@
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L75" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C75,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C75,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M75" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C75,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C75,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N75" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C75,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C75,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O75" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C75,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C75,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P75" s="10">
-        <f>IF(ISNUMBER(L75),IF(L75=0,"n.a.",N75/L75),"n.a.")</f>
-        <v/>
+      <c r="L75" s="9" t="n">
+        <v>18107.39</v>
+      </c>
+      <c r="M75" s="9" t="n">
+        <v>-17600.19</v>
+      </c>
+      <c r="N75" s="9" t="n">
+        <v>-17839.84</v>
+      </c>
+      <c r="O75" s="9" t="n">
+        <v>-18501.77</v>
+      </c>
+      <c r="P75" s="10" t="n">
+        <v>-0.9852242647891276</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -4404,25 +4317,20 @@
       <c r="K76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L76" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C76,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C76,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M76" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C76,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C76,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N76" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C76,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C76,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O76" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C76,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C76,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P76" s="10">
-        <f>IF(ISNUMBER(L76),IF(L76=0,"n.a.",N76/L76),"n.a.")</f>
-        <v/>
+      <c r="L76" s="9" t="n">
+        <v>758485.8100000001</v>
+      </c>
+      <c r="M76" s="9" t="n">
+        <v>-118906.75</v>
+      </c>
+      <c r="N76" s="9" t="n">
+        <v>-126130.62</v>
+      </c>
+      <c r="O76" s="9" t="n">
+        <v>-153857.71</v>
+      </c>
+      <c r="P76" s="10" t="n">
+        <v>-0.166292656153976</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -4455,25 +4363,20 @@
       <c r="K77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L77" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C77,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C77,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M77" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C77,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C77,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N77" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C77,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C77,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O77" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C77,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C77,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P77" s="10">
-        <f>IF(ISNUMBER(L77),IF(L77=0,"n.a.",N77/L77),"n.a.")</f>
-        <v/>
+      <c r="L77" s="9" t="n">
+        <v>23745</v>
+      </c>
+      <c r="M77" s="9" t="n">
+        <v>7778</v>
+      </c>
+      <c r="N77" s="9" t="n">
+        <v>7779.88</v>
+      </c>
+      <c r="O77" s="9" t="n">
+        <v>6911.86</v>
+      </c>
+      <c r="P77" s="10" t="n">
+        <v>0.3276428721836176</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4506,25 +4409,20 @@
       <c r="K78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L78" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C78,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C78,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M78" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C78,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C78,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N78" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C78,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C78,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O78" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C78,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C78,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P78" s="10">
-        <f>IF(ISNUMBER(L78),IF(L78=0,"n.a.",N78/L78),"n.a.")</f>
-        <v/>
+      <c r="L78" s="9" t="n">
+        <v>16000</v>
+      </c>
+      <c r="M78" s="9" t="n">
+        <v>7882.97</v>
+      </c>
+      <c r="N78" s="9" t="n">
+        <v>7882.97</v>
+      </c>
+      <c r="O78" s="9" t="n">
+        <v>7298.08</v>
+      </c>
+      <c r="P78" s="10" t="n">
+        <v>0.492685625</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4557,25 +4455,20 @@
       <c r="K79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L79" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C79,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C79,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M79" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C79,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C79,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N79" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C79,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C79,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O79" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C79,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C79,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P79" s="10">
-        <f>IF(ISNUMBER(L79),IF(L79=0,"n.a.",N79/L79),"n.a.")</f>
-        <v/>
+      <c r="L79" s="9" t="n">
+        <v>15250</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>7057.91</v>
+      </c>
+      <c r="N79" s="9" t="n">
+        <v>7057.91</v>
+      </c>
+      <c r="O79" s="9" t="n">
+        <v>6500.43</v>
+      </c>
+      <c r="P79" s="10" t="n">
+        <v>0.4628137704918033</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4608,25 +4501,20 @@
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L80" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C80,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C80,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M80" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C80,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C80,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N80" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C80,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C80,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O80" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C80,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C80,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P80" s="10">
-        <f>IF(ISNUMBER(L80),IF(L80=0,"n.a.",N80/L80),"n.a.")</f>
-        <v/>
+      <c r="L80" s="9" t="n">
+        <v>220000</v>
+      </c>
+      <c r="M80" s="9" t="n">
+        <v>122000</v>
+      </c>
+      <c r="N80" s="9" t="n">
+        <v>122000</v>
+      </c>
+      <c r="O80" s="9" t="n">
+        <v>113957.71</v>
+      </c>
+      <c r="P80" s="10" t="n">
+        <v>0.5545454545454546</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4659,25 +4547,20 @@
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C81,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C81,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M81" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C81,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C81,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N81" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C81,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C81,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O81" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C81,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C81,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P81" s="10">
-        <f>IF(ISNUMBER(L81),IF(L81=0,"n.a.",N81/L81),"n.a.")</f>
-        <v/>
+      <c r="L81" s="9" t="n">
+        <v>-10600</v>
+      </c>
+      <c r="M81" s="9" t="n">
+        <v>-38861.42</v>
+      </c>
+      <c r="N81" s="9" t="n">
+        <v>-39364.56</v>
+      </c>
+      <c r="O81" s="9" t="n">
+        <v>-39364.56</v>
+      </c>
+      <c r="P81" s="10" t="n">
+        <v>3.713637735849056</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4710,25 +4593,22 @@
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L82" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C82,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C82,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M82" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C82,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C82,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N82" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C82,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C82,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O82" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C82,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C82,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P82" s="10">
-        <f>IF(ISNUMBER(L82),IF(L82=0,"n.a.",N82/L82),"n.a.")</f>
-        <v/>
+      <c r="L82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="9" t="n">
+        <v>-2737.24</v>
+      </c>
+      <c r="N82" s="9" t="n">
+        <v>-2739.46</v>
+      </c>
+      <c r="O82" s="9" t="n">
+        <v>-2739.46</v>
+      </c>
+      <c r="P82" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4761,25 +4641,30 @@
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L83" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C83,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C83,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M83" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C83,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C83,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N83" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C83,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C83,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O83" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C83,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C83,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P83" s="10">
-        <f>IF(ISNUMBER(L83),IF(L83=0,"n.a.",N83/L83),"n.a.")</f>
-        <v/>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M83" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N83" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O83" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P83" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4812,25 +4697,30 @@
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L84" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C84,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C84,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M84" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C84,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C84,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N84" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C84,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C84,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O84" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C84,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C84,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P84" s="10">
-        <f>IF(ISNUMBER(L84),IF(L84=0,"n.a.",N84/L84),"n.a.")</f>
-        <v/>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M84" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N84" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O84" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P84" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4863,25 +4753,22 @@
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L85" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C85,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C85,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M85" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C85,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C85,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N85" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C85,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C85,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O85" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C85,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C85,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P85" s="10">
-        <f>IF(ISNUMBER(L85),IF(L85=0,"n.a.",N85/L85),"n.a.")</f>
-        <v/>
+      <c r="L85" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="9" t="n">
+        <v>-5293.57</v>
+      </c>
+      <c r="N85" s="9" t="n">
+        <v>-5293.57</v>
+      </c>
+      <c r="O85" s="9" t="n">
+        <v>-5293.57</v>
+      </c>
+      <c r="P85" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4914,25 +4801,20 @@
       <c r="K86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L86" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C86,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C86,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M86" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C86,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C86,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N86" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C86,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C86,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O86" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C86,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C86,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P86" s="10">
-        <f>IF(ISNUMBER(L86),IF(L86=0,"n.a.",N86/L86),"n.a.")</f>
-        <v/>
+      <c r="L86" s="9" t="n">
+        <v>1055.73</v>
+      </c>
+      <c r="M86" s="9" t="n">
+        <v>-8698.790000000001</v>
+      </c>
+      <c r="N86" s="9" t="n">
+        <v>-8715.889999999999</v>
+      </c>
+      <c r="O86" s="9" t="n">
+        <v>-8754.48</v>
+      </c>
+      <c r="P86" s="10" t="n">
+        <v>-8.255794568687069</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4965,25 +4847,20 @@
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L87" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C87,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C87,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M87" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C87,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C87,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N87" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C87,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C87,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O87" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C87,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C87,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P87" s="10">
-        <f>IF(ISNUMBER(L87),IF(L87=0,"n.a.",N87/L87),"n.a.")</f>
-        <v/>
+      <c r="L87" s="9" t="n">
+        <v>16839.08</v>
+      </c>
+      <c r="M87" s="9" t="n">
+        <v>2858.07</v>
+      </c>
+      <c r="N87" s="9" t="n">
+        <v>1239.45</v>
+      </c>
+      <c r="O87" s="9" t="n">
+        <v>623.88</v>
+      </c>
+      <c r="P87" s="10" t="n">
+        <v>0.07360556514963999</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -5016,25 +4893,20 @@
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L88" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C88,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C88,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M88" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C88,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C88,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N88" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C88,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C88,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O88" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C88,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C88,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P88" s="10">
-        <f>IF(ISNUMBER(L88),IF(L88=0,"n.a.",N88/L88),"n.a.")</f>
-        <v/>
+      <c r="L88" s="9" t="n">
+        <v>2991108.78</v>
+      </c>
+      <c r="M88" s="9" t="n">
+        <v>796621.49</v>
+      </c>
+      <c r="N88" s="9" t="n">
+        <v>769022.14</v>
+      </c>
+      <c r="O88" s="9" t="n">
+        <v>659679.64</v>
+      </c>
+      <c r="P88" s="10" t="n">
+        <v>0.2571026988861301</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -5067,25 +4939,20 @@
       <c r="K89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L89" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C89,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C89,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M89" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C89,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C89,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N89" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C89,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C89,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O89" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C89,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C89,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P89" s="10">
-        <f>IF(ISNUMBER(L89),IF(L89=0,"n.a.",N89/L89),"n.a.")</f>
-        <v/>
+      <c r="L89" s="9" t="n">
+        <v>98017.2</v>
+      </c>
+      <c r="M89" s="9" t="n">
+        <v>63589.08</v>
+      </c>
+      <c r="N89" s="9" t="n">
+        <v>60602.44</v>
+      </c>
+      <c r="O89" s="9" t="n">
+        <v>57019.34</v>
+      </c>
+      <c r="P89" s="10" t="n">
+        <v>0.6182837297943626</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -5118,25 +4985,20 @@
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L90" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C90,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C90,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M90" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C90,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C90,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N90" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C90,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C90,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O90" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C90,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C90,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P90" s="10">
-        <f>IF(ISNUMBER(L90),IF(L90=0,"n.a.",N90/L90),"n.a.")</f>
-        <v/>
+      <c r="L90" s="9" t="n">
+        <v>231904.97</v>
+      </c>
+      <c r="M90" s="9" t="n">
+        <v>174965.05</v>
+      </c>
+      <c r="N90" s="9" t="n">
+        <v>173734.5</v>
+      </c>
+      <c r="O90" s="9" t="n">
+        <v>165257.02</v>
+      </c>
+      <c r="P90" s="10" t="n">
+        <v>0.7491624694373734</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -5169,25 +5031,22 @@
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L91" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C91,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C91,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M91" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C91,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C91,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N91" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C91,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C91,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O91" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C91,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C91,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P91" s="10">
-        <f>IF(ISNUMBER(L91),IF(L91=0,"n.a.",N91/L91),"n.a.")</f>
-        <v/>
+      <c r="L91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -5220,25 +5079,20 @@
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L92" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C92,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C92,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M92" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C92,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C92,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N92" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C92,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C92,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O92" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C92,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C92,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P92" s="10">
-        <f>IF(ISNUMBER(L92),IF(L92=0,"n.a.",N92/L92),"n.a.")</f>
-        <v/>
+      <c r="L92" s="9" t="n">
+        <v>52101.99</v>
+      </c>
+      <c r="M92" s="9" t="n">
+        <v>19611.8</v>
+      </c>
+      <c r="N92" s="9" t="n">
+        <v>7874.98</v>
+      </c>
+      <c r="O92" s="9" t="n">
+        <v>5970.35</v>
+      </c>
+      <c r="P92" s="10" t="n">
+        <v>0.1511454744818768</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -5271,25 +5125,30 @@
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L93" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C93,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C93,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M93" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C93,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C93,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N93" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C93,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C93,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O93" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C93,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C93,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P93" s="10">
-        <f>IF(ISNUMBER(L93),IF(L93=0,"n.a.",N93/L93),"n.a.")</f>
-        <v/>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M93" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N93" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O93" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P93" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -5322,25 +5181,30 @@
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L94" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C94,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C94,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M94" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C94,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C94,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N94" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C94,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C94,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O94" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C94,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C94,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P94" s="10">
-        <f>IF(ISNUMBER(L94),IF(L94=0,"n.a.",N94/L94),"n.a.")</f>
-        <v/>
+      <c r="L94" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M94" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N94" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O94" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P94" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -5373,25 +5237,30 @@
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L95" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C95,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C95,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M95" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C95,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C95,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N95" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C95,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C95,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O95" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C95,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C95,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P95" s="10">
-        <f>IF(ISNUMBER(L95),IF(L95=0,"n.a.",N95/L95),"n.a.")</f>
-        <v/>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M95" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N95" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O95" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P95" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -5424,25 +5293,30 @@
       <c r="K96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L96" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C96,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C96,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M96" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C96,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C96,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N96" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C96,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C96,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O96" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C96,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C96,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P96" s="10">
-        <f>IF(ISNUMBER(L96),IF(L96=0,"n.a.",N96/L96),"n.a.")</f>
-        <v/>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M96" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N96" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O96" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P96" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
@@ -5475,25 +5349,30 @@
       <c r="K97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L97" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C97,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C97,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M97" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C97,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C97,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N97" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C97,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C97,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O97" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C97,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C97,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P97" s="10">
-        <f>IF(ISNUMBER(L97),IF(L97=0,"n.a.",N97/L97),"n.a.")</f>
-        <v/>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M97" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N97" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O97" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P97" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
@@ -5526,25 +5405,30 @@
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L98" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C98,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C98,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M98" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C98,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C98,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N98" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C98,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C98,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O98" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C98,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C98,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P98" s="10">
-        <f>IF(ISNUMBER(L98),IF(L98=0,"n.a.",N98/L98),"n.a.")</f>
-        <v/>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O98" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P98" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
@@ -5577,25 +5461,22 @@
       <c r="K99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L99" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C99,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C99,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M99" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C99,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C99,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N99" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C99,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C99,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O99" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C99,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C99,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P99" s="10">
-        <f>IF(ISNUMBER(L99),IF(L99=0,"n.a.",N99/L99),"n.a.")</f>
-        <v/>
+      <c r="L99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="N99" s="9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="O99" s="9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="P99" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
@@ -5628,25 +5509,20 @@
       <c r="K100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L100" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C100,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C100,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M100" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C100,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C100,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N100" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C100,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C100,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O100" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C100,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C100,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P100" s="10">
-        <f>IF(ISNUMBER(L100),IF(L100=0,"n.a.",N100/L100),"n.a.")</f>
-        <v/>
+      <c r="L100" s="9" t="n">
+        <v>8250</v>
+      </c>
+      <c r="M100" s="9" t="n">
+        <v>8250</v>
+      </c>
+      <c r="N100" s="9" t="n">
+        <v>8250</v>
+      </c>
+      <c r="O100" s="9" t="n">
+        <v>7948.41</v>
+      </c>
+      <c r="P100" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
@@ -5679,25 +5555,20 @@
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L101" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C101,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C101,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M101" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C101,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C101,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N101" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C101,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C101,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O101" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C101,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C101,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P101" s="10">
-        <f>IF(ISNUMBER(L101),IF(L101=0,"n.a.",N101/L101),"n.a.")</f>
-        <v/>
+      <c r="L101" s="9" t="n">
+        <v>-122785.46</v>
+      </c>
+      <c r="M101" s="9" t="n">
+        <v>-122785.46</v>
+      </c>
+      <c r="N101" s="9" t="n">
+        <v>-122788.76</v>
+      </c>
+      <c r="O101" s="9" t="n">
+        <v>-122788.76</v>
+      </c>
+      <c r="P101" s="10" t="n">
+        <v>1.00002687614641</v>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
@@ -5730,25 +5601,20 @@
       <c r="K102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L102" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C102,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C102,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M102" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C102,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C102,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N102" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C102,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C102,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O102" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C102,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C102,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P102" s="10">
-        <f>IF(ISNUMBER(L102),IF(L102=0,"n.a.",N102/L102),"n.a.")</f>
-        <v/>
+      <c r="L102" s="9" t="n">
+        <v>475.29</v>
+      </c>
+      <c r="M102" s="9" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="N102" s="9" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="O102" s="9" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="P102" s="10" t="n">
+        <v>0.1071345915125502</v>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
@@ -5781,25 +5647,20 @@
       <c r="K103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L103" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C103,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C103,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M103" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C103,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C103,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N103" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C103,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C103,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O103" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C103,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C103,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P103" s="10">
-        <f>IF(ISNUMBER(L103),IF(L103=0,"n.a.",N103/L103),"n.a.")</f>
-        <v/>
+      <c r="L103" s="9" t="n">
+        <v>527418.28</v>
+      </c>
+      <c r="M103" s="9" t="n">
+        <v>136266.83</v>
+      </c>
+      <c r="N103" s="9" t="n">
+        <v>135344.02</v>
+      </c>
+      <c r="O103" s="9" t="n">
+        <v>116063.8</v>
+      </c>
+      <c r="P103" s="10" t="n">
+        <v>0.256616096051885</v>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
@@ -5832,25 +5693,30 @@
       <c r="K104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L104" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C104,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C104,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M104" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C104,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C104,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N104" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C104,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C104,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O104" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C104,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C104,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P104" s="10">
-        <f>IF(ISNUMBER(L104),IF(L104=0,"n.a.",N104/L104),"n.a.")</f>
-        <v/>
+      <c r="L104" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M104" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N104" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O104" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P104" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
@@ -5883,25 +5749,30 @@
       <c r="K105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L105" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C105,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C105,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M105" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C105,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C105,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N105" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C105,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C105,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O105" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C105,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C105,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P105" s="10">
-        <f>IF(ISNUMBER(L105),IF(L105=0,"n.a.",N105/L105),"n.a.")</f>
-        <v/>
+      <c r="L105" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M105" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N105" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O105" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P105" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
@@ -5934,25 +5805,30 @@
       <c r="K106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L106" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C106,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C106,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M106" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C106,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C106,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N106" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C106,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C106,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O106" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C106,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C106,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P106" s="10">
-        <f>IF(ISNUMBER(L106),IF(L106=0,"n.a.",N106/L106),"n.a.")</f>
-        <v/>
+      <c r="L106" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M106" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N106" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O106" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P106" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
@@ -5985,25 +5861,30 @@
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L107" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C107,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C107,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M107" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C107,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C107,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N107" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C107,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C107,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O107" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C107,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C107,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P107" s="10">
-        <f>IF(ISNUMBER(L107),IF(L107=0,"n.a.",N107/L107),"n.a.")</f>
-        <v/>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O107" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P107" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
@@ -6036,25 +5917,30 @@
       <c r="K108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L108" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C108,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C108,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M108" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C108,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C108,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N108" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C108,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C108,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O108" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C108,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C108,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P108" s="10">
-        <f>IF(ISNUMBER(L108),IF(L108=0,"n.a.",N108/L108),"n.a.")</f>
-        <v/>
+      <c r="L108" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M108" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N108" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O108" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P108" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
@@ -6087,25 +5973,30 @@
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L109" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C109,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C109,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M109" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C109,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C109,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N109" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C109,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C109,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O109" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C109,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C109,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P109" s="10">
-        <f>IF(ISNUMBER(L109),IF(L109=0,"n.a.",N109/L109),"n.a.")</f>
-        <v/>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M109" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O109" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P109" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
@@ -6138,25 +6029,30 @@
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L110" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C110,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C110,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M110" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C110,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C110,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N110" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C110,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C110,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O110" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C110,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C110,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P110" s="10">
-        <f>IF(ISNUMBER(L110),IF(L110=0,"n.a.",N110/L110),"n.a.")</f>
-        <v/>
+      <c r="L110" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M110" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N110" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O110" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P110" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
@@ -6189,25 +6085,30 @@
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L111" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C111,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C111,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M111" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C111,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C111,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N111" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C111,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C111,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O111" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C111,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C111,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P111" s="10">
-        <f>IF(ISNUMBER(L111),IF(L111=0,"n.a.",N111/L111),"n.a.")</f>
-        <v/>
+      <c r="L111" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M111" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N111" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O111" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P111" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1">
@@ -6240,25 +6141,30 @@
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L112" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C112,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C112,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M112" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C112,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C112,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N112" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C112,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C112,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O112" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C112,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C112,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P112" s="10">
-        <f>IF(ISNUMBER(L112),IF(L112=0,"n.a.",N112/L112),"n.a.")</f>
-        <v/>
+      <c r="L112" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M112" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N112" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O112" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P112" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
@@ -6291,25 +6197,30 @@
       <c r="K113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L113" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C113,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C113,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M113" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C113,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C113,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N113" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C113,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C113,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O113" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C113,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C113,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P113" s="10">
-        <f>IF(ISNUMBER(L113),IF(L113=0,"n.a.",N113/L113),"n.a.")</f>
-        <v/>
+      <c r="L113" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M113" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N113" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O113" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P113" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1">
@@ -6342,25 +6253,30 @@
       <c r="K114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L114" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C114,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C114,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M114" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C114,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C114,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N114" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C114,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C114,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O114" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C114,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C114,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P114" s="10">
-        <f>IF(ISNUMBER(L114),IF(L114=0,"n.a.",N114/L114),"n.a.")</f>
-        <v/>
+      <c r="L114" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M114" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N114" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O114" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P114" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1">
@@ -6393,25 +6309,30 @@
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L115" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C115,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C115,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M115" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C115,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C115,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N115" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C115,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C115,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O115" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C115,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C115,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P115" s="10">
-        <f>IF(ISNUMBER(L115),IF(L115=0,"n.a.",N115/L115),"n.a.")</f>
-        <v/>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M115" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N115" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O115" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P115" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1">
@@ -6444,25 +6365,30 @@
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L116" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C116,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C116,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M116" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C116,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C116,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N116" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C116,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C116,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O116" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C116,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C116,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P116" s="10">
-        <f>IF(ISNUMBER(L116),IF(L116=0,"n.a.",N116/L116),"n.a.")</f>
-        <v/>
+      <c r="L116" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M116" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N116" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O116" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P116" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="117" ht="21" customHeight="1">
@@ -6495,25 +6421,30 @@
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L117" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C117,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C117,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M117" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C117,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C117,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N117" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C117,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C117,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O117" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C117,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C117,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P117" s="10">
-        <f>IF(ISNUMBER(L117),IF(L117=0,"n.a.",N117/L117),"n.a.")</f>
-        <v/>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M117" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N117" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O117" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P117" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="118" ht="21" customHeight="1">
@@ -6546,25 +6477,30 @@
       <c r="K118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L118" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C118,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C118,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M118" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C118,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C118,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N118" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C118,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C118,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O118" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C118,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C118,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P118" s="10">
-        <f>IF(ISNUMBER(L118),IF(L118=0,"n.a.",N118/L118),"n.a.")</f>
-        <v/>
+      <c r="L118" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M118" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N118" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O118" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P118" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="119" ht="21" customHeight="1">
@@ -6597,25 +6533,30 @@
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L119" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C119,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C119,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M119" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C119,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C119,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N119" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C119,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C119,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O119" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C119,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C119,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P119" s="10">
-        <f>IF(ISNUMBER(L119),IF(L119=0,"n.a.",N119/L119),"n.a.")</f>
-        <v/>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M119" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N119" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O119" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P119" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="120" ht="21" customHeight="1">
@@ -6648,25 +6589,30 @@
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L120" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C120,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C120,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M120" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C120,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C120,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N120" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C120,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C120,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O120" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C120,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C120,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P120" s="10">
-        <f>IF(ISNUMBER(L120),IF(L120=0,"n.a.",N120/L120),"n.a.")</f>
-        <v/>
+      <c r="L120" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M120" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N120" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O120" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P120" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="121" ht="21" customHeight="1">
@@ -6699,25 +6645,30 @@
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L121" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C121,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C121,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M121" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C121,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C121,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N121" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C121,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C121,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O121" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C121,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C121,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P121" s="10">
-        <f>IF(ISNUMBER(L121),IF(L121=0,"n.a.",N121/L121),"n.a.")</f>
-        <v/>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M121" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N121" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O121" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P121" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="122" ht="21" customHeight="1">
@@ -6750,25 +6701,30 @@
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L122" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C122,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C122,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M122" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C122,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C122,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N122" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C122,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C122,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O122" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C122,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C122,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P122" s="10">
-        <f>IF(ISNUMBER(L122),IF(L122=0,"n.a.",N122/L122),"n.a.")</f>
-        <v/>
+      <c r="L122" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M122" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N122" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O122" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P122" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="123" ht="21" customHeight="1">
@@ -6801,25 +6757,30 @@
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L123" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C123,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C123,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M123" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C123,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C123,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N123" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C123,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C123,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O123" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C123,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C123,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P123" s="10">
-        <f>IF(ISNUMBER(L123),IF(L123=0,"n.a.",N123/L123),"n.a.")</f>
-        <v/>
+      <c r="L123" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M123" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N123" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O123" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P123" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="124" ht="21" customHeight="1">
@@ -6852,25 +6813,30 @@
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L124" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C124,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C124,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M124" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C124,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C124,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N124" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C124,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C124,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O124" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C124,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C124,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P124" s="10">
-        <f>IF(ISNUMBER(L124),IF(L124=0,"n.a.",N124/L124),"n.a.")</f>
-        <v/>
+      <c r="L124" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M124" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N124" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O124" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P124" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="125" ht="21" customHeight="1">
@@ -6903,25 +6869,30 @@
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L125" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C125,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C125,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M125" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C125,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C125,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N125" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C125,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C125,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O125" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C125,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C125,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P125" s="10">
-        <f>IF(ISNUMBER(L125),IF(L125=0,"n.a.",N125/L125),"n.a.")</f>
-        <v/>
+      <c r="L125" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M125" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N125" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O125" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P125" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="126" ht="21" customHeight="1">
@@ -6954,25 +6925,30 @@
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L126" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C126,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C126,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M126" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C126,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C126,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N126" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C126,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C126,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O126" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C126,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C126,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P126" s="10">
-        <f>IF(ISNUMBER(L126),IF(L126=0,"n.a.",N126/L126),"n.a.")</f>
-        <v/>
+      <c r="L126" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M126" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N126" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O126" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P126" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="127" ht="21" customHeight="1">
@@ -7005,25 +6981,30 @@
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L127" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C127,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C127,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M127" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C127,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C127,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N127" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C127,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C127,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O127" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C127,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C127,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P127" s="10">
-        <f>IF(ISNUMBER(L127),IF(L127=0,"n.a.",N127/L127),"n.a.")</f>
-        <v/>
+      <c r="L127" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M127" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N127" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O127" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P127" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="128" ht="21" customHeight="1">
@@ -7056,25 +7037,30 @@
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L128" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C128,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C128,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M128" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C128,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C128,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N128" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C128,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C128,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O128" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C128,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C128,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P128" s="10">
-        <f>IF(ISNUMBER(L128),IF(L128=0,"n.a.",N128/L128),"n.a.")</f>
-        <v/>
+      <c r="L128" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M128" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N128" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O128" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P128" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="129" ht="21" customHeight="1">
@@ -7107,25 +7093,30 @@
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L129" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C129,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C129,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M129" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C129,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C129,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N129" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C129,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C129,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O129" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C129,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C129,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P129" s="10">
-        <f>IF(ISNUMBER(L129),IF(L129=0,"n.a.",N129/L129),"n.a.")</f>
-        <v/>
+      <c r="L129" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M129" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N129" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O129" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P129" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="130" ht="21" customHeight="1">
@@ -7166,25 +7157,30 @@
       <c r="K130" s="9" t="n">
         <v>540000</v>
       </c>
-      <c r="L130" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C130,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C130,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M130" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C130,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C130,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N130" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C130,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C130,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O130" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C130,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C130,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P130" s="10">
-        <f>IF(ISNUMBER(L130),IF(L130=0,"n.a.",N130/L130),"n.a.")</f>
-        <v/>
+      <c r="L130" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M130" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N130" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O130" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P130" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="131" ht="21" customHeight="1">
@@ -7225,25 +7221,30 @@
       <c r="K131" s="9" t="n">
         <v>200000</v>
       </c>
-      <c r="L131" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C131,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C131,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M131" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C131,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C131,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N131" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C131,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C131,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O131" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C131,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C131,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P131" s="10">
-        <f>IF(ISNUMBER(L131),IF(L131=0,"n.a.",N131/L131),"n.a.")</f>
-        <v/>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M131" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N131" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O131" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P131" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="132" ht="21" customHeight="1">
@@ -7284,25 +7285,20 @@
       <c r="K132" s="9" t="n">
         <v>292110</v>
       </c>
-      <c r="L132" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C132,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C132,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M132" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C132,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C132,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N132" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C132,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C132,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O132" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C132,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C132,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P132" s="10">
-        <f>IF(ISNUMBER(L132),IF(L132=0,"n.a.",N132/L132),"n.a.")</f>
-        <v/>
+      <c r="L132" s="9" t="n">
+        <v>132500</v>
+      </c>
+      <c r="M132" s="9" t="n">
+        <v>16058.75</v>
+      </c>
+      <c r="N132" s="9" t="n">
+        <v>15285.11</v>
+      </c>
+      <c r="O132" s="9" t="n">
+        <v>10441.46</v>
+      </c>
+      <c r="P132" s="10" t="n">
+        <v>0.115359320754717</v>
       </c>
     </row>
     <row r="133" ht="21" customHeight="1">
@@ -7335,25 +7331,22 @@
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L133" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C133,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C133,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M133" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C133,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C133,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N133" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C133,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C133,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O133" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C133,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C133,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P133" s="10">
-        <f>IF(ISNUMBER(L133),IF(L133=0,"n.a.",N133/L133),"n.a.")</f>
-        <v/>
+      <c r="L133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="9" t="n">
+        <v>-14534.01</v>
+      </c>
+      <c r="N133" s="9" t="n">
+        <v>-15149.12</v>
+      </c>
+      <c r="O133" s="9" t="n">
+        <v>-15149.12</v>
+      </c>
+      <c r="P133" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="134" ht="21" customHeight="1">
@@ -7386,25 +7379,22 @@
       <c r="K134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L134" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C134,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C134,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M134" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C134,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C134,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N134" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C134,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C134,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O134" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C134,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C134,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P134" s="10">
-        <f>IF(ISNUMBER(L134),IF(L134=0,"n.a.",N134/L134),"n.a.")</f>
-        <v/>
+      <c r="L134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="9" t="n">
+        <v>-7654</v>
+      </c>
+      <c r="N134" s="9" t="n">
+        <v>-7750.89</v>
+      </c>
+      <c r="O134" s="9" t="n">
+        <v>-7750.89</v>
+      </c>
+      <c r="P134" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="135" ht="21" customHeight="1">
@@ -7437,25 +7427,20 @@
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L135" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C135,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C135,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M135" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C135,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C135,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N135" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C135,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C135,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O135" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C135,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C135,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P135" s="10">
-        <f>IF(ISNUMBER(L135),IF(L135=0,"n.a.",N135/L135),"n.a.")</f>
-        <v/>
+      <c r="L135" s="9" t="n">
+        <v>9367.07</v>
+      </c>
+      <c r="M135" s="9" t="n">
+        <v>5095.48</v>
+      </c>
+      <c r="N135" s="9" t="n">
+        <v>4594.86</v>
+      </c>
+      <c r="O135" s="9" t="n">
+        <v>4252.44</v>
+      </c>
+      <c r="P135" s="10" t="n">
+        <v>0.4905333257891742</v>
       </c>
     </row>
     <row r="136" ht="21" customHeight="1">
@@ -7488,25 +7473,30 @@
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L136" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C136,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C136,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M136" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C136,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C136,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N136" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C136,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C136,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O136" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C136,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C136,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P136" s="10">
-        <f>IF(ISNUMBER(L136),IF(L136=0,"n.a.",N136/L136),"n.a.")</f>
-        <v/>
+      <c r="L136" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M136" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N136" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O136" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P136" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="137" ht="21" customHeight="1">
@@ -7539,25 +7529,30 @@
       <c r="K137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L137" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C137,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C137,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M137" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C137,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C137,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N137" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C137,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C137,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O137" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C137,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C137,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P137" s="10">
-        <f>IF(ISNUMBER(L137),IF(L137=0,"n.a.",N137/L137),"n.a.")</f>
-        <v/>
+      <c r="L137" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M137" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N137" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O137" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P137" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="138" ht="21" customHeight="1">
@@ -7590,25 +7585,30 @@
       <c r="K138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L138" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C138,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C138,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M138" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C138,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C138,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N138" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C138,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C138,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O138" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C138,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C138,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P138" s="10">
-        <f>IF(ISNUMBER(L138),IF(L138=0,"n.a.",N138/L138),"n.a.")</f>
-        <v/>
+      <c r="L138" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M138" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N138" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O138" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P138" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="139" ht="21" customHeight="1">
@@ -7641,25 +7641,30 @@
       <c r="K139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L139" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C139,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C139,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M139" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C139,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C139,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N139" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C139,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C139,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O139" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C139,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C139,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P139" s="10">
-        <f>IF(ISNUMBER(L139),IF(L139=0,"n.a.",N139/L139),"n.a.")</f>
-        <v/>
+      <c r="L139" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M139" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N139" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O139" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P139" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="140" ht="21" customHeight="1">
@@ -7692,25 +7697,30 @@
       <c r="K140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L140" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C140,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C140,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M140" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C140,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C140,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N140" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C140,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C140,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O140" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C140,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C140,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P140" s="10">
-        <f>IF(ISNUMBER(L140),IF(L140=0,"n.a.",N140/L140),"n.a.")</f>
-        <v/>
+      <c r="L140" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M140" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N140" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O140" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P140" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="141" ht="21" customHeight="1">
@@ -7743,25 +7753,20 @@
       <c r="K141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L141" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C141,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C141,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M141" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C141,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C141,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N141" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C141,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C141,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O141" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C141,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C141,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P141" s="10">
-        <f>IF(ISNUMBER(L141),IF(L141=0,"n.a.",N141/L141),"n.a.")</f>
-        <v/>
+      <c r="L141" s="9" t="n">
+        <v>-25780.46</v>
+      </c>
+      <c r="M141" s="9" t="n">
+        <v>-25780.46</v>
+      </c>
+      <c r="N141" s="9" t="n">
+        <v>-25780.46</v>
+      </c>
+      <c r="O141" s="9" t="n">
+        <v>-25780.46</v>
+      </c>
+      <c r="P141" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="142" ht="21" customHeight="1">
@@ -7794,25 +7799,20 @@
       <c r="K142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L142" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C142,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C142,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M142" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C142,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C142,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N142" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C142,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C142,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O142" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C142,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C142,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P142" s="10">
-        <f>IF(ISNUMBER(L142),IF(L142=0,"n.a.",N142/L142),"n.a.")</f>
-        <v/>
+      <c r="L142" s="9" t="n">
+        <v>-8740.15</v>
+      </c>
+      <c r="M142" s="9" t="n">
+        <v>-26735.61</v>
+      </c>
+      <c r="N142" s="9" t="n">
+        <v>-26735.61</v>
+      </c>
+      <c r="O142" s="9" t="n">
+        <v>-26735.61</v>
+      </c>
+      <c r="P142" s="10" t="n">
+        <v>3.058941780175398</v>
       </c>
     </row>
     <row r="143" ht="21" customHeight="1">
@@ -7845,25 +7845,20 @@
       <c r="K143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L143" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C143,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C143,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M143" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C143,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C143,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N143" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C143,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C143,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O143" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C143,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C143,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P143" s="10">
-        <f>IF(ISNUMBER(L143),IF(L143=0,"n.a.",N143/L143),"n.a.")</f>
-        <v/>
+      <c r="L143" s="9" t="n">
+        <v>29755.02</v>
+      </c>
+      <c r="M143" s="9" t="n">
+        <v>-1244.98</v>
+      </c>
+      <c r="N143" s="9" t="n">
+        <v>-1244.98</v>
+      </c>
+      <c r="O143" s="9" t="n">
+        <v>-2332.7</v>
+      </c>
+      <c r="P143" s="10" t="n">
+        <v>-0.04184100699646648</v>
       </c>
     </row>
     <row r="144" ht="21" customHeight="1">
@@ -7896,25 +7891,22 @@
       <c r="K144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L144" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C144,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C144,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M144" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C144,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C144,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N144" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C144,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C144,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O144" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C144,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C144,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P144" s="10">
-        <f>IF(ISNUMBER(L144),IF(L144=0,"n.a.",N144/L144),"n.a.")</f>
-        <v/>
+      <c r="L144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="9" t="n">
+        <v>-166.84</v>
+      </c>
+      <c r="N144" s="9" t="n">
+        <v>-166.84</v>
+      </c>
+      <c r="O144" s="9" t="n">
+        <v>-166.84</v>
+      </c>
+      <c r="P144" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="145" ht="21" customHeight="1">
@@ -7947,25 +7939,20 @@
       <c r="K145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L145" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C145,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C145,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M145" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C145,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C145,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N145" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C145,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C145,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O145" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C145,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C145,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P145" s="10">
-        <f>IF(ISNUMBER(L145),IF(L145=0,"n.a.",N145/L145),"n.a.")</f>
-        <v/>
+      <c r="L145" s="9" t="n">
+        <v>40236.26</v>
+      </c>
+      <c r="M145" s="9" t="n">
+        <v>8788.82</v>
+      </c>
+      <c r="N145" s="9" t="n">
+        <v>8788.82</v>
+      </c>
+      <c r="O145" s="9" t="n">
+        <v>7317.95</v>
+      </c>
+      <c r="P145" s="10" t="n">
+        <v>0.2184303411897627</v>
       </c>
     </row>
     <row r="146" ht="21" customHeight="1">
@@ -7998,25 +7985,20 @@
       <c r="K146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L146" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C146,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C146,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M146" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C146,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C146,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N146" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C146,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C146,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O146" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C146,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C146,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P146" s="10">
-        <f>IF(ISNUMBER(L146),IF(L146=0,"n.a.",N146/L146),"n.a.")</f>
-        <v/>
+      <c r="L146" s="9" t="n">
+        <v>14290.34</v>
+      </c>
+      <c r="M146" s="9" t="n">
+        <v>14290.34</v>
+      </c>
+      <c r="N146" s="9" t="n">
+        <v>14290.34</v>
+      </c>
+      <c r="O146" s="9" t="n">
+        <v>13767.94</v>
+      </c>
+      <c r="P146" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="147" ht="21" customHeight="1">
@@ -8049,25 +8031,20 @@
       <c r="K147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L147" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C147,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C147,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M147" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C147,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C147,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N147" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C147,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C147,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O147" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C147,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C147,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P147" s="10">
-        <f>IF(ISNUMBER(L147),IF(L147=0,"n.a.",N147/L147),"n.a.")</f>
-        <v/>
+      <c r="L147" s="9" t="n">
+        <v>45525.16</v>
+      </c>
+      <c r="M147" s="9" t="n">
+        <v>14925.16</v>
+      </c>
+      <c r="N147" s="9" t="n">
+        <v>14925.16</v>
+      </c>
+      <c r="O147" s="9" t="n">
+        <v>13260.95</v>
+      </c>
+      <c r="P147" s="10" t="n">
+        <v>0.3278442074668161</v>
       </c>
     </row>
     <row r="148" ht="21" customHeight="1">
@@ -8100,25 +8077,20 @@
       <c r="K148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L148" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C148,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C148,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M148" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C148,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C148,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N148" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C148,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C148,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O148" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C148,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C148,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P148" s="10">
-        <f>IF(ISNUMBER(L148),IF(L148=0,"n.a.",N148/L148),"n.a.")</f>
-        <v/>
+      <c r="L148" s="9" t="n">
+        <v>13933.04</v>
+      </c>
+      <c r="M148" s="9" t="n">
+        <v>-8125.38</v>
+      </c>
+      <c r="N148" s="9" t="n">
+        <v>-8125.38</v>
+      </c>
+      <c r="O148" s="9" t="n">
+        <v>-8634.709999999999</v>
+      </c>
+      <c r="P148" s="10" t="n">
+        <v>-0.5831735213564304</v>
       </c>
     </row>
     <row r="149" ht="21" customHeight="1">
@@ -8151,25 +8123,20 @@
       <c r="K149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L149" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C149,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C149,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M149" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C149,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C149,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N149" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C149,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C149,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O149" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C149,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C149,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P149" s="10">
-        <f>IF(ISNUMBER(L149),IF(L149=0,"n.a.",N149/L149),"n.a.")</f>
-        <v/>
+      <c r="L149" s="9" t="n">
+        <v>72370.00999999999</v>
+      </c>
+      <c r="M149" s="9" t="n">
+        <v>-70340.19</v>
+      </c>
+      <c r="N149" s="9" t="n">
+        <v>-70340.19</v>
+      </c>
+      <c r="O149" s="9" t="n">
+        <v>-72985.74000000001</v>
+      </c>
+      <c r="P149" s="10" t="n">
+        <v>-0.9719521940096458</v>
       </c>
     </row>
     <row r="150" ht="21" customHeight="1">
@@ -8202,25 +8169,20 @@
       <c r="K150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L150" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C150,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C150,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M150" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C150,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C150,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N150" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C150,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C150,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O150" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C150,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C150,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P150" s="10">
-        <f>IF(ISNUMBER(L150),IF(L150=0,"n.a.",N150/L150),"n.a.")</f>
-        <v/>
+      <c r="L150" s="9" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="M150" s="9" t="n">
+        <v>-138.33</v>
+      </c>
+      <c r="N150" s="9" t="n">
+        <v>-138.33</v>
+      </c>
+      <c r="O150" s="9" t="n">
+        <v>-140.15</v>
+      </c>
+      <c r="P150" s="10" t="n">
+        <v>-2.774368231046932</v>
       </c>
     </row>
     <row r="151" ht="21" customHeight="1">
@@ -8253,25 +8215,20 @@
       <c r="K151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L151" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C151,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C151,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M151" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C151,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C151,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N151" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C151,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C151,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O151" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C151,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C151,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P151" s="10">
-        <f>IF(ISNUMBER(L151),IF(L151=0,"n.a.",N151/L151),"n.a.")</f>
-        <v/>
+      <c r="L151" s="9" t="n">
+        <v>12625.47</v>
+      </c>
+      <c r="M151" s="9" t="n">
+        <v>-3540.01</v>
+      </c>
+      <c r="N151" s="9" t="n">
+        <v>-3540.01</v>
+      </c>
+      <c r="O151" s="9" t="n">
+        <v>-4001.54</v>
+      </c>
+      <c r="P151" s="10" t="n">
+        <v>-0.2803863935362407</v>
       </c>
     </row>
     <row r="152" ht="21" customHeight="1">
@@ -8304,25 +8261,30 @@
       <c r="K152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L152" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C152,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C152,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M152" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C152,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C152,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N152" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C152,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C152,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O152" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C152,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C152,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P152" s="10">
-        <f>IF(ISNUMBER(L152),IF(L152=0,"n.a.",N152/L152),"n.a.")</f>
-        <v/>
+      <c r="L152" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M152" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N152" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O152" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P152" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="153" ht="21" customHeight="1">
@@ -8355,25 +8317,20 @@
       <c r="K153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L153" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C153,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C153,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M153" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C153,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C153,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N153" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C153,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C153,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O153" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C153,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C153,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P153" s="10">
-        <f>IF(ISNUMBER(L153),IF(L153=0,"n.a.",N153/L153),"n.a.")</f>
-        <v/>
+      <c r="L153" s="9" t="n">
+        <v>-46266.37</v>
+      </c>
+      <c r="M153" s="9" t="n">
+        <v>-59781.89</v>
+      </c>
+      <c r="N153" s="9" t="n">
+        <v>-59781.89</v>
+      </c>
+      <c r="O153" s="9" t="n">
+        <v>-59781.89</v>
+      </c>
+      <c r="P153" s="10" t="n">
+        <v>1.29212406333153</v>
       </c>
     </row>
     <row r="154" ht="21" customHeight="1">
@@ -8406,25 +8363,20 @@
       <c r="K154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L154" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C154,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C154,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M154" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C154,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C154,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N154" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C154,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C154,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O154" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C154,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C154,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P154" s="10">
-        <f>IF(ISNUMBER(L154),IF(L154=0,"n.a.",N154/L154),"n.a.")</f>
-        <v/>
+      <c r="L154" s="9" t="n">
+        <v>16030.23</v>
+      </c>
+      <c r="M154" s="9" t="n">
+        <v>13558.38</v>
+      </c>
+      <c r="N154" s="9" t="n">
+        <v>13322.18</v>
+      </c>
+      <c r="O154" s="9" t="n">
+        <v>12736.18</v>
+      </c>
+      <c r="P154" s="10" t="n">
+        <v>0.8310660545731409</v>
       </c>
     </row>
     <row r="155" ht="21" customHeight="1">
@@ -8457,25 +8409,20 @@
       <c r="K155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L155" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C155,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C155,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M155" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C155,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C155,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N155" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C155,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C155,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O155" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C155,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C155,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P155" s="10">
-        <f>IF(ISNUMBER(L155),IF(L155=0,"n.a.",N155/L155),"n.a.")</f>
-        <v/>
+      <c r="L155" s="9" t="n">
+        <v>5236.57</v>
+      </c>
+      <c r="M155" s="9" t="n">
+        <v>5236.57</v>
+      </c>
+      <c r="N155" s="9" t="n">
+        <v>5236.57</v>
+      </c>
+      <c r="O155" s="9" t="n">
+        <v>5045.14</v>
+      </c>
+      <c r="P155" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1">
@@ -8508,25 +8455,20 @@
       <c r="K156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L156" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C156,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C156,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M156" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C156,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C156,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N156" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C156,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C156,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O156" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C156,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C156,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P156" s="10">
-        <f>IF(ISNUMBER(L156),IF(L156=0,"n.a.",N156/L156),"n.a.")</f>
-        <v/>
+      <c r="L156" s="9" t="n">
+        <v>37284</v>
+      </c>
+      <c r="M156" s="9" t="n">
+        <v>37284</v>
+      </c>
+      <c r="N156" s="9" t="n">
+        <v>37284</v>
+      </c>
+      <c r="O156" s="9" t="n">
+        <v>35921.05</v>
+      </c>
+      <c r="P156" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="157" ht="21" customHeight="1">
@@ -8559,25 +8501,20 @@
       <c r="K157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L157" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C157,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C157,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M157" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C157,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C157,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N157" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C157,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C157,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O157" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C157,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C157,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P157" s="10">
-        <f>IF(ISNUMBER(L157),IF(L157=0,"n.a.",N157/L157),"n.a.")</f>
-        <v/>
+      <c r="L157" s="9" t="n">
+        <v>-5683.12</v>
+      </c>
+      <c r="M157" s="9" t="n">
+        <v>-5683.12</v>
+      </c>
+      <c r="N157" s="9" t="n">
+        <v>-5683.12</v>
+      </c>
+      <c r="O157" s="9" t="n">
+        <v>-5683.12</v>
+      </c>
+      <c r="P157" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="158" ht="21" customHeight="1">
@@ -8610,25 +8547,22 @@
       <c r="K158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L158" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C158,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C158,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M158" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C158,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C158,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N158" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C158,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C158,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O158" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C158,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C158,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P158" s="10">
-        <f>IF(ISNUMBER(L158),IF(L158=0,"n.a.",N158/L158),"n.a.")</f>
-        <v/>
+      <c r="L158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="159" ht="21" customHeight="1">
@@ -8661,25 +8595,20 @@
       <c r="K159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L159" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C159,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C159,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M159" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C159,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C159,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N159" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C159,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C159,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O159" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C159,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C159,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P159" s="10">
-        <f>IF(ISNUMBER(L159),IF(L159=0,"n.a.",N159/L159),"n.a.")</f>
-        <v/>
+      <c r="L159" s="9" t="n">
+        <v>7269.84</v>
+      </c>
+      <c r="M159" s="9" t="n">
+        <v>7269.84</v>
+      </c>
+      <c r="N159" s="9" t="n">
+        <v>7269.84</v>
+      </c>
+      <c r="O159" s="9" t="n">
+        <v>7004.08</v>
+      </c>
+      <c r="P159" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1">
@@ -8712,25 +8641,22 @@
       <c r="K160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L160" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C160,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C160,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M160" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C160,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C160,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N160" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C160,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C160,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O160" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C160,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C160,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P160" s="10">
-        <f>IF(ISNUMBER(L160),IF(L160=0,"n.a.",N160/L160),"n.a.")</f>
-        <v/>
+      <c r="L160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" s="9" t="n">
+        <v>-189.05</v>
+      </c>
+      <c r="O160" s="9" t="n">
+        <v>-189.05</v>
+      </c>
+      <c r="P160" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="161" ht="21" customHeight="1">
@@ -8763,25 +8689,22 @@
       <c r="K161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L161" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C161,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C161,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M161" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C161,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C161,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N161" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C161,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C161,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O161" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C161,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C161,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P161" s="10">
-        <f>IF(ISNUMBER(L161),IF(L161=0,"n.a.",N161/L161),"n.a.")</f>
-        <v/>
+      <c r="L161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="162" ht="21" customHeight="1">
@@ -8814,25 +8737,22 @@
       <c r="K162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L162" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C162,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C162,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M162" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C162,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C162,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N162" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C162,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C162,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O162" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C162,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C162,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P162" s="10">
-        <f>IF(ISNUMBER(L162),IF(L162=0,"n.a.",N162/L162),"n.a.")</f>
-        <v/>
+      <c r="L162" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="9" t="n">
+        <v>-583.34</v>
+      </c>
+      <c r="N162" s="9" t="n">
+        <v>-583.34</v>
+      </c>
+      <c r="O162" s="9" t="n">
+        <v>-583.34</v>
+      </c>
+      <c r="P162" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="163" ht="21" customHeight="1">
@@ -8865,25 +8785,22 @@
       <c r="K163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L163" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C163,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C163,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M163" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C163,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C163,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N163" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C163,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C163,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O163" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C163,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C163,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P163" s="10">
-        <f>IF(ISNUMBER(L163),IF(L163=0,"n.a.",N163/L163),"n.a.")</f>
-        <v/>
+      <c r="L163" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="9" t="n">
+        <v>-2952.15</v>
+      </c>
+      <c r="N163" s="9" t="n">
+        <v>-3096.72</v>
+      </c>
+      <c r="O163" s="9" t="n">
+        <v>-3096.72</v>
+      </c>
+      <c r="P163" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1">
@@ -8916,25 +8833,20 @@
       <c r="K164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L164" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C164,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C164,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M164" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C164,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C164,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N164" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C164,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C164,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O164" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C164,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C164,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P164" s="10">
-        <f>IF(ISNUMBER(L164),IF(L164=0,"n.a.",N164/L164),"n.a.")</f>
-        <v/>
+      <c r="L164" s="9" t="n">
+        <v>-591.8099999999999</v>
+      </c>
+      <c r="M164" s="9" t="n">
+        <v>-804.28</v>
+      </c>
+      <c r="N164" s="9" t="n">
+        <v>-870.84</v>
+      </c>
+      <c r="O164" s="9" t="n">
+        <v>-870.84</v>
+      </c>
+      <c r="P164" s="10" t="n">
+        <v>1.471485780909414</v>
       </c>
     </row>
     <row r="165" ht="21" customHeight="1">
@@ -8967,25 +8879,20 @@
       <c r="K165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L165" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C165,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C165,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M165" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C165,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C165,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N165" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C165,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C165,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O165" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C165,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C165,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P165" s="10">
-        <f>IF(ISNUMBER(L165),IF(L165=0,"n.a.",N165/L165),"n.a.")</f>
-        <v/>
+      <c r="L165" s="9" t="n">
+        <v>28224.24</v>
+      </c>
+      <c r="M165" s="9" t="n">
+        <v>8360.049999999999</v>
+      </c>
+      <c r="N165" s="9" t="n">
+        <v>8155.8</v>
+      </c>
+      <c r="O165" s="9" t="n">
+        <v>7124.04</v>
+      </c>
+      <c r="P165" s="10" t="n">
+        <v>0.2889643795545956</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1">
@@ -9018,25 +8925,20 @@
       <c r="K166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L166" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C166,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C166,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M166" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C166,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C166,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N166" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C166,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C166,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O166" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C166,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C166,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P166" s="10">
-        <f>IF(ISNUMBER(L166),IF(L166=0,"n.a.",N166/L166),"n.a.")</f>
-        <v/>
+      <c r="L166" s="9" t="n">
+        <v>5542.71</v>
+      </c>
+      <c r="M166" s="9" t="n">
+        <v>4986.26</v>
+      </c>
+      <c r="N166" s="9" t="n">
+        <v>4986.26</v>
+      </c>
+      <c r="O166" s="9" t="n">
+        <v>4783.64</v>
+      </c>
+      <c r="P166" s="10" t="n">
+        <v>0.8996068710071428</v>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1">
@@ -9069,25 +8971,20 @@
       <c r="K167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L167" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C167,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C167,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M167" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C167,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C167,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N167" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C167,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C167,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O167" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C167,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C167,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P167" s="10">
-        <f>IF(ISNUMBER(L167),IF(L167=0,"n.a.",N167/L167),"n.a.")</f>
-        <v/>
+      <c r="L167" s="9" t="n">
+        <v>6059.53</v>
+      </c>
+      <c r="M167" s="9" t="n">
+        <v>6059.53</v>
+      </c>
+      <c r="N167" s="9" t="n">
+        <v>6059.53</v>
+      </c>
+      <c r="O167" s="9" t="n">
+        <v>5838.02</v>
+      </c>
+      <c r="P167" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1">
@@ -9120,25 +9017,22 @@
       <c r="K168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L168" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C168,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C168,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M168" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C168,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C168,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N168" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C168,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C168,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O168" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C168,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C168,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P168" s="10">
-        <f>IF(ISNUMBER(L168),IF(L168=0,"n.a.",N168/L168),"n.a.")</f>
-        <v/>
+      <c r="L168" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="9" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="N168" s="9" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="O168" s="9" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="P168" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1">
@@ -9171,25 +9065,20 @@
       <c r="K169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L169" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C169,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C169,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M169" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C169,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C169,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N169" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C169,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C169,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O169" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C169,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C169,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P169" s="10">
-        <f>IF(ISNUMBER(L169),IF(L169=0,"n.a.",N169/L169),"n.a.")</f>
-        <v/>
+      <c r="L169" s="9" t="n">
+        <v>-2847.73</v>
+      </c>
+      <c r="M169" s="9" t="n">
+        <v>-2847.73</v>
+      </c>
+      <c r="N169" s="9" t="n">
+        <v>-2847.73</v>
+      </c>
+      <c r="O169" s="9" t="n">
+        <v>-2847.73</v>
+      </c>
+      <c r="P169" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1">
@@ -9222,25 +9111,20 @@
       <c r="K170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L170" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C170,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C170,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M170" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C170,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C170,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N170" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C170,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C170,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O170" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C170,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C170,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P170" s="10">
-        <f>IF(ISNUMBER(L170),IF(L170=0,"n.a.",N170/L170),"n.a.")</f>
-        <v/>
+      <c r="L170" s="9" t="n">
+        <v>81006.27</v>
+      </c>
+      <c r="M170" s="9" t="n">
+        <v>81006.27</v>
+      </c>
+      <c r="N170" s="9" t="n">
+        <v>81006.27</v>
+      </c>
+      <c r="O170" s="9" t="n">
+        <v>78045.02</v>
+      </c>
+      <c r="P170" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="171" ht="21" customHeight="1">
@@ -9273,25 +9157,22 @@
       <c r="K171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L171" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C171,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C171,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M171" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C171,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C171,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N171" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C171,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C171,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O171" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C171,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C171,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P171" s="10">
-        <f>IF(ISNUMBER(L171),IF(L171=0,"n.a.",N171/L171),"n.a.")</f>
-        <v/>
+      <c r="L171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="172" ht="21" customHeight="1">
@@ -9324,25 +9205,20 @@
       <c r="K172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L172" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C172,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C172,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M172" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C172,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C172,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N172" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C172,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C172,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O172" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C172,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C172,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P172" s="10">
-        <f>IF(ISNUMBER(L172),IF(L172=0,"n.a.",N172/L172),"n.a.")</f>
-        <v/>
+      <c r="L172" s="9" t="n">
+        <v>-39809.7</v>
+      </c>
+      <c r="M172" s="9" t="n">
+        <v>-39793.65</v>
+      </c>
+      <c r="N172" s="9" t="n">
+        <v>-39800.73</v>
+      </c>
+      <c r="O172" s="9" t="n">
+        <v>-39800.73</v>
+      </c>
+      <c r="P172" s="10" t="n">
+        <v>0.9997746780307314</v>
       </c>
     </row>
     <row r="173" ht="21" customHeight="1">
@@ -9375,25 +9251,22 @@
       <c r="K173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L173" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C173,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C173,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M173" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C173,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C173,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N173" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C173,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C173,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O173" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C173,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C173,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P173" s="10">
-        <f>IF(ISNUMBER(L173),IF(L173=0,"n.a.",N173/L173),"n.a.")</f>
-        <v/>
+      <c r="L173" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N173" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O173" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P173" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
     </row>
     <row r="174" ht="21" customHeight="1">
@@ -9430,27 +9303,34 @@
       <c r="K174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L174" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C174,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$G$8:$G$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C174,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="M174" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C174,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$O$8:$O$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C174,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="N174" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C174,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$Q$8:$Q$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C174,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="O174" s="9">
-        <f>IF(COUNTIFS('[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C174,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6)=0,"n.a.",SUMIFS('[D Projekte.xlsx]D Projekte'!$S$8:$S$107,'[D Projekte.xlsx]D Projekte'!$C$8:$C$107,C174,'[D Projekte.xlsx]D Projekte'!$A$8:$A$107,'[Steuerung.xlsx]Steuerung'!$F$6))</f>
-        <v/>
-      </c>
-      <c r="P174" s="10">
-        <f>IF(ISNUMBER(L174),IF(L174=0,"n.a.",N174/L174),"n.a.")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="L174" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="M174" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="N174" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="O174" s="9" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="P174" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175"/>
+    <row r="176"/>
     <row r="177">
       <c r="C177" t="inlineStr">
         <is>
